--- a/amc_book/Quant Mutual Fund/Quant Small Cap Fund - _G_/FACT_SHEET_2026-06-25.xlsx
+++ b/amc_book/Quant Mutual Fund/Quant Small Cap Fund - _G_/FACT_SHEET_2026-06-25.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>INE068V01023</t>
+          <t>INE548A01028</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Gland Pharma Limited</t>
+          <t>HFCL Limited</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -614,38 +614,38 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3895867</v>
+        <v>41137732</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>2314.8</v>
+        <v>215</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>901.8153</v>
+        <v>884.4612</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>2314.8</v>
+        <v>215</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>901.8153</v>
+        <v>884.4612</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>2326.2</v>
+        <v>204.77</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>906.2566</v>
+        <v>842.3773</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>-0.4901</v>
+        <v>4.9958</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>-0.01447</v>
+        <v>0.14468</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>2.9529</v>
+        <v>2.896</v>
       </c>
     </row>
     <row r="7">
@@ -654,12 +654,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>INE614B01018</t>
+          <t>INE676A01027</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Karnataka Bank Ltd</t>
+          <t>Black Box Limited</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -669,38 +669,38 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>33600200</v>
+        <v>8297643</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>265.6</v>
+        <v>957.9</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>892.4213</v>
+        <v>794.8312</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>265.6</v>
+        <v>957.9</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>892.4213</v>
+        <v>794.8312</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>265.15</v>
+        <v>986.5</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>890.9093</v>
+        <v>818.5625</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.1697</v>
+        <v>-2.8991</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>0.00496</v>
+        <v>-0.07545</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>2.9221</v>
+        <v>2.6026</v>
       </c>
     </row>
     <row r="8">
@@ -709,12 +709,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>INE202B01038</t>
+          <t>INE191B01025</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Piramal Finance Ltd</t>
+          <t>Welspun Corp Limited</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -728,34 +728,34 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>4143723</v>
+        <v>4751987</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>2131</v>
+        <v>1455.1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>883.0273999999999</v>
+        <v>691.4616</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>2131</v>
+        <v>1455.1</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>883.0273999999999</v>
+        <v>691.4616</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>2134.8</v>
+        <v>1406</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>884.602</v>
+        <v>668.1294</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>-0.178</v>
+        <v>3.4922</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>-0.00515</v>
+        <v>0.07907</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>2.8913</v>
+        <v>2.2641</v>
       </c>
     </row>
     <row r="9">
@@ -764,12 +764,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>INE208C01025</t>
+          <t>INE614B01018</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Aegis Logistics Limited</t>
+          <t>Karnataka Bank Ltd</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>7576729</v>
+        <v>25160520</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1140.65</v>
+        <v>265.6</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>864.2396</v>
+        <v>668.2634</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1140.65</v>
+        <v>265.6</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>864.2396</v>
+        <v>668.2634</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1062.9</v>
+        <v>265.15</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>805.3305</v>
+        <v>667.1312</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>7.3149</v>
+        <v>0.1697</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>0.207</v>
+        <v>0.00371</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>2.8298</v>
+        <v>2.1881</v>
       </c>
     </row>
     <row r="10">
@@ -819,12 +819,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>INE191B01025</t>
+          <t>INE281B01032</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Welspun Corp Limited</t>
+          <t>Lloyds Metals And Energy Limited</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -838,34 +838,34 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>5616590</v>
+        <v>3841957</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1455.1</v>
+        <v>1721.4</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>817.27</v>
+        <v>661.3545</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1455.1</v>
+        <v>1721.4</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>817.27</v>
+        <v>661.3545</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>1406</v>
+        <v>1704.3</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>789.6926</v>
+        <v>654.7847</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>3.4922</v>
+        <v>1.0033</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>0.09345000000000001</v>
+        <v>0.02173</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>2.676</v>
+        <v>2.1655</v>
       </c>
     </row>
     <row r="11">
@@ -874,12 +874,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>INE914M01019</t>
+          <t>INE034A01011</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Aster DM Healthcare Limited</t>
+          <t>Arvind Limited</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -893,34 +893,34 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>10567247</v>
+        <v>11946217</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>769.05</v>
+        <v>547.25</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>812.6741</v>
+        <v>653.7567</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>769.05</v>
+        <v>547.25</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>812.6741</v>
+        <v>653.7567</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>769.7</v>
+        <v>556.1</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>813.361</v>
+        <v>664.3291</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>-0.0844</v>
+        <v>-1.5914</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>-0.00225</v>
+        <v>-0.03407</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>2.661</v>
+        <v>2.1406</v>
       </c>
     </row>
     <row r="12">
@@ -929,12 +929,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>INE522D01027</t>
+          <t>INE068V01023</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Manappuram Finance Ltd</t>
+          <t>Gland Pharma Limited</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -948,34 +948,34 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>25365028</v>
+        <v>2748538</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>318.5</v>
+        <v>2314.8</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>807.8761</v>
+        <v>636.2316</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>318.5</v>
+        <v>2314.8</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>807.8761</v>
+        <v>636.2316</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>318.35</v>
+        <v>2326.2</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>807.4957000000001</v>
+        <v>639.3649</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>0.0471</v>
+        <v>-0.4901</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>0.00125</v>
+        <v>-0.01021</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>2.6453</v>
+        <v>2.0832</v>
       </c>
     </row>
     <row r="13">
@@ -1003,34 +1003,34 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>11775287</v>
+        <v>9127053</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>678.1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>798.4822</v>
+        <v>618.9055</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>678.1</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>798.4822</v>
+        <v>618.9055</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>663</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>780.7015</v>
+        <v>605.1236</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>2.2775</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>0.05955</v>
+        <v>0.04615</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>2.6145</v>
+        <v>2.0265</v>
       </c>
     </row>
     <row r="14">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>INE281B01032</t>
+          <t>INE364U01010</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Lloyds Metals And Energy Limited</t>
+          <t>Adani Green Energy Limited</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1058,34 +1058,34 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>4147421</v>
+        <v>3964721</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1721.4</v>
+        <v>1526.1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>713.9371</v>
+        <v>605.0561</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1721.4</v>
+        <v>1526.1</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>713.9371</v>
+        <v>605.0561</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>1704.3</v>
+        <v>1525.4</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>706.845</v>
+        <v>604.7785</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1.0033</v>
+        <v>0.0459</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>0.02345</v>
+        <v>0.00091</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>2.3377</v>
+        <v>1.9812</v>
       </c>
     </row>
     <row r="15">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>INE364U01010</t>
+          <t>INE495B01038</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Adani Green Energy Limited</t>
+          <t>Suven Life Sciences Ltd.</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1109,38 +1109,38 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>4616625</v>
+        <v>22230013</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1526.1</v>
+        <v>267.25</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>704.5431</v>
+        <v>594.0971</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1526.1</v>
+        <v>267.25</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>704.5431</v>
+        <v>594.0971</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>1525.4</v>
+        <v>254.7</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>704.22</v>
+        <v>566.1984</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0459</v>
+        <v>4.9274</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>0.00106</v>
+        <v>0.09585</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>2.3069</v>
+        <v>1.9453</v>
       </c>
     </row>
     <row r="16">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>INE676A01027</t>
+          <t>INE814H01029</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Black Box Limited</t>
+          <t>Adani Power Limited</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1164,38 +1164,38 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>7158945</v>
+        <v>25868271</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>957.9</v>
+        <v>229.27</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>685.7553</v>
+        <v>593.0818</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>957.9</v>
+        <v>229.27</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>685.7553</v>
+        <v>593.0818</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>986.5</v>
+        <v>229.76</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>706.2299</v>
+        <v>594.3493999999999</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>-2.8991</v>
+        <v>-0.2133</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.00414</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>2.2454</v>
+        <v>1.942</v>
       </c>
     </row>
     <row r="17">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>INE780C01023</t>
+          <t>INE202B01038</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>JM FINANCIAL LIMITED</t>
+          <t>Piramal Finance Ltd</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1219,38 +1219,38 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>54507219</v>
+        <v>2700554</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>125.81</v>
+        <v>2131</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>685.7553</v>
+        <v>575.4881</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>125.81</v>
+        <v>2131</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>685.7553</v>
+        <v>575.4881</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>126</v>
+        <v>2134.8</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>686.7910000000001</v>
+        <v>576.5143</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>-0.1508</v>
+        <v>-0.178</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>-0.00339</v>
+        <v>-0.00335</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>2.2454</v>
+        <v>1.8844</v>
       </c>
     </row>
     <row r="18">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>INE180C01042</t>
+          <t>INE522D01027</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Capri Global Capital Limited</t>
+          <t>Manappuram Finance Ltd</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1274,38 +1274,38 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>31105658</v>
+        <v>17972092</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>217.44</v>
+        <v>318.5</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>676.3614</v>
+        <v>572.4111</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>217.44</v>
+        <v>318.5</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>676.3614</v>
+        <v>572.4111</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>218.39</v>
+        <v>318.35</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>679.3165</v>
+        <v>572.1415</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>-0.435</v>
+        <v>0.0471</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>-0.00963</v>
+        <v>0.00088</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>2.2146</v>
+        <v>1.8743</v>
       </c>
     </row>
     <row r="19">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>INE034A01011</t>
+          <t>INE775A01035</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Arvind Limited</t>
+          <t>Samvardhana Motherson International Ltd</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1329,38 +1329,38 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>11946217</v>
+        <v>36269281</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>547.25</v>
+        <v>151.71</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>653.7567</v>
+        <v>550.2413</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>547.25</v>
+        <v>151.71</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>653.7567</v>
+        <v>550.2413</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>556.1</v>
+        <v>144.58</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>664.3291</v>
+        <v>524.3813</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>-1.5914</v>
+        <v>4.9315</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>-0.03407</v>
+        <v>0.08885</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>2.1406</v>
+        <v>1.8017</v>
       </c>
     </row>
     <row r="20">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>INE775A01035</t>
+          <t>INE914M01019</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd</t>
+          <t>Aster DM Healthcare Limited</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>42724916</v>
+        <v>7084942</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>151.71</v>
+        <v>769.05</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>648.1797</v>
+        <v>544.8674999999999</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>151.71</v>
+        <v>769.05</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>648.1797</v>
+        <v>544.8674999999999</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>144.58</v>
+        <v>769.7</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>617.7168</v>
+        <v>545.328</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>4.9315</v>
+        <v>-0.0844</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>0.10467</v>
+        <v>-0.00151</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>2.1224</v>
+        <v>1.7841</v>
       </c>
     </row>
     <row r="21">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>3805403</v>
+        <v>3386446</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1555.2</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>591.8163</v>
+        <v>526.6601000000001</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>1555.2</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>591.8163</v>
+        <v>526.6601000000001</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>1530.6</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>582.455</v>
+        <v>518.3294</v>
       </c>
       <c r="M21" s="9" t="n">
         <v>1.6072</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0.03114</v>
+        <v>0.02772</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>1.9378</v>
+        <v>1.7245</v>
       </c>
     </row>
     <row r="22">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>INE423A01024</t>
+          <t>INE0CZ201020</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Adani Enterprises Limited</t>
+          <t>ANTHEM BIOSCIENCES LIMITED</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1494,38 +1494,38 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1917124</v>
+        <v>6796196</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>3038</v>
+        <v>761.7</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>582.4223</v>
+        <v>517.6662</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>3038</v>
+        <v>761.7</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>582.4223</v>
+        <v>517.6662</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>3069.7</v>
+        <v>767.0859</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>588.4996</v>
+        <v>521.3266</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>-1.0327</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>-0.01969</v>
+        <v>-0.0119</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>1.9071</v>
+        <v>1.695</v>
       </c>
     </row>
     <row r="23">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>INE090A01021</t>
+          <t>INE423A01024</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>Adani Enterprises Limited</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1553,34 +1553,34 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4129935</v>
+        <v>1681907</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1387.5</v>
+        <v>3038</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>573.0285</v>
+        <v>510.9633</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1387.5</v>
+        <v>3038</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>573.0285</v>
+        <v>510.9633</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>1373.6</v>
+        <v>3069.7</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>567.2879</v>
+        <v>516.295</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>1.0119</v>
+        <v>-1.0327</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0.01899</v>
+        <v>-0.01728</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>1.8763</v>
+        <v>1.6731</v>
       </c>
     </row>
     <row r="24">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>INE0CZ201020</t>
+          <t>INE777F01014</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>ANTHEM BIOSCIENCES LIMITED</t>
+          <t>Exicom Tele-Systems Limited</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1604,38 +1604,38 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>6796196</v>
+        <v>32308234</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>761.7</v>
+        <v>158.07</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>517.6662</v>
+        <v>510.6963</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>761.7</v>
+        <v>158.07</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>517.6662</v>
+        <v>510.6963</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>767.0859</v>
+        <v>165.06</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>521.3266</v>
+        <v>533.2797</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-4.2348</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>-0.0119</v>
+        <v>-0.07081</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>1.695</v>
+        <v>1.6722</v>
       </c>
     </row>
     <row r="25">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>INE930H01031</t>
+          <t>INE152M01016</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>K.P.R. Mill Limited</t>
+          <t>Triveni Turbine Limited</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1663,34 +1663,34 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4258130</v>
+        <v>7497262</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1191.3</v>
+        <v>669.35</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>507.271</v>
+        <v>501.8292</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1191.3</v>
+        <v>669.35</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>507.271</v>
+        <v>501.8292</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>1218.45</v>
+        <v>675.55</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>518.8318</v>
+        <v>506.4775</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>-2.2282</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>-0.03701</v>
+        <v>-0.01508</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>1.661</v>
+        <v>1.6432</v>
       </c>
     </row>
     <row r="26">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>INE306R01017</t>
+          <t>INE208C01025</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Intellect Design Arena Limited</t>
+          <t>Aegis Logistics Limited</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1714,38 +1714,38 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>6427482</v>
+        <v>4267726</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>747.05</v>
+        <v>1140.65</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>480.165</v>
+        <v>486.7982</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>747.05</v>
+        <v>1140.65</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>480.165</v>
+        <v>486.7982</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>755.35</v>
+        <v>1062.9</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>485.4999</v>
+        <v>453.6166</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>-1.0988</v>
+        <v>7.3149</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>-0.01728</v>
+        <v>0.11659</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>1.5722</v>
+        <v>1.5939</v>
       </c>
     </row>
     <row r="27">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>INE548A01028</t>
+          <t>INE780C01023</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>HFCL Limited</t>
+          <t>JM FINANCIAL LIMITED</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1773,34 +1773,34 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>21846299</v>
+        <v>38446710</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>215</v>
+        <v>125.81</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>469.6954</v>
+        <v>483.6981</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>215</v>
+        <v>125.81</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>469.6954</v>
+        <v>483.6981</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>204.77</v>
+        <v>126</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>447.3467</v>
+        <v>484.4285</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>4.9958</v>
+        <v>-0.1508</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>0.07683</v>
+        <v>-0.00239</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>1.5379</v>
+        <v>1.5838</v>
       </c>
     </row>
     <row r="28">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>INE495B01038</t>
+          <t>INE371A01025</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Suven Life Sciences Ltd.</t>
+          <t>Graphite India Limited</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1824,38 +1824,38 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>17575133</v>
+        <v>7907518</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>267.25</v>
+        <v>605.8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>469.6954</v>
+        <v>479.0374</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>267.25</v>
+        <v>605.8</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>469.6954</v>
+        <v>479.0374</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>254.7</v>
+        <v>622.85</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>447.6386</v>
+        <v>492.5198</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>4.9274</v>
+        <v>-2.7374</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>0.07578</v>
+        <v>-0.04294</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>1.5379</v>
+        <v>1.5685</v>
       </c>
     </row>
     <row r="29">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>INE777F01014</t>
+          <t>INE180C01042</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Exicom Tele-Systems Limited</t>
+          <t>Capri Global Capital Limited</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1883,34 +1883,34 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>29714394</v>
+        <v>21543475</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>158.07</v>
+        <v>217.44</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>469.6954</v>
+        <v>468.4413</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>158.07</v>
+        <v>217.44</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>469.6954</v>
+        <v>468.4413</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>165.06</v>
+        <v>218.39</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>490.4658</v>
+        <v>470.488</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>-4.2348</v>
+        <v>-0.435</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>-0.06512999999999999</v>
+        <v>-0.00667</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>1.5379</v>
+        <v>1.5338</v>
       </c>
     </row>
     <row r="30">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>INE002A01018</t>
+          <t>INE119A01028</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Reliance Industries Limited</t>
+          <t>Balrampur Chini Mills Limited</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1938,34 +1938,34 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>3492159</v>
+        <v>8746159</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>1318.1</v>
+        <v>534.2</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>460.3015</v>
+        <v>467.2198</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1318.1</v>
+        <v>534.2</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>460.3015</v>
+        <v>467.2198</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1313.6</v>
+        <v>536.8</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>458.73</v>
+        <v>469.4938</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>0.3426</v>
+        <v>-0.4844</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v>0.00516</v>
+        <v>-0.00741</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>1.5072</v>
+        <v>1.5298</v>
       </c>
     </row>
     <row r="31">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>INE152M01016</t>
+          <t>INE228A01035</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Triveni Turbine Limited</t>
+          <t>Usha Martin Limited</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1993,34 +1993,34 @@
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>6596156</v>
+        <v>9163497</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>669.35</v>
+        <v>473.1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>441.5137</v>
+        <v>433.525</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>669.35</v>
+        <v>473.1</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>441.5137</v>
+        <v>433.525</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>675.55</v>
+        <v>465.8</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>445.6033</v>
+        <v>426.8357</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>-0.9177999999999999</v>
+        <v>1.5672</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>-0.01327</v>
+        <v>0.02225</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>1.4457</v>
+        <v>1.4195</v>
       </c>
     </row>
     <row r="32">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>INE647O01011</t>
+          <t>INE807F01027</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Aditya Birla Fashion And Retail Ltd</t>
+          <t>Viyash Scientific Limited</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2044,38 +2044,38 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>72785807</v>
+        <v>16081297</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>60.12</v>
+        <v>269.3</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>437.5883</v>
+        <v>433.0693</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>60.12</v>
+        <v>269.3</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>437.5883</v>
+        <v>433.0693</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>61.6</v>
+        <v>271.25</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>448.3606</v>
+        <v>436.2052</v>
       </c>
       <c r="M32" s="9" t="n">
-        <v>-2.4026</v>
+        <v>-0.7189</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>-0.03442</v>
+        <v>-0.01019</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>1.4328</v>
+        <v>1.418</v>
       </c>
     </row>
     <row r="33">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>INE228A01035</t>
+          <t>INE073K01018</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Usha Martin Limited</t>
+          <t>Sona BLW Precision Forgings Limited</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2099,38 +2099,38 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>9163497</v>
+        <v>6869745</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>473.1</v>
+        <v>619.25</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>433.525</v>
+        <v>425.409</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>473.1</v>
+        <v>619.25</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>433.525</v>
+        <v>425.409</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>465.8</v>
+        <v>619.2999</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>426.8357</v>
+        <v>425.4432</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>1.5672</v>
+        <v>-0.0081</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>0.02225</v>
+        <v>-0.00011</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>1.4195</v>
+        <v>1.3929</v>
       </c>
     </row>
     <row r="34">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>INE795G01014</t>
+          <t>INE090A01021</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Co Ltd</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2158,34 +2158,34 @@
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>7060073</v>
+        <v>3061838</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>585.45</v>
+        <v>1387.5</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>413.332</v>
+        <v>424.83</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>585.45</v>
+        <v>1387.5</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>413.332</v>
+        <v>424.83</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>591.75</v>
+        <v>1373.6</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>417.7798</v>
+        <v>420.5741</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>-1.0646</v>
+        <v>1.0119</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>-0.01441</v>
+        <v>0.01408</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>1.3534</v>
+        <v>1.391</v>
       </c>
     </row>
     <row r="35">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>INE205C01021</t>
+          <t>INE463V01026</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Poly Medicure Limited</t>
+          <t>Anand Rathi Wealth Limited</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2209,38 +2209,38 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2474175</v>
+        <v>2157689</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>1650.2</v>
+        <v>1932.5</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>408.2884</v>
+        <v>416.9734</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1650.2</v>
+        <v>1932.5</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>408.2884</v>
+        <v>416.9734</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>1650.9</v>
+        <v>1903.9</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>408.4616</v>
+        <v>410.8024</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>-0.0424</v>
+        <v>1.5022</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>-0.00057</v>
+        <v>0.02051</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>1.3369</v>
+        <v>1.3653</v>
       </c>
     </row>
     <row r="36">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>INE949H01023</t>
+          <t>INE976G01028</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Man Infraconstruction Limited</t>
+          <t>RBL Bank Limited</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2374,38 +2374,38 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>37148453</v>
+        <v>10548538</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>104.38</v>
+        <v>371.05</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>387.7556</v>
+        <v>391.4035</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>104.38</v>
+        <v>371.05</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>387.7556</v>
+        <v>391.4035</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>104.69</v>
+        <v>377.05</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>388.9072</v>
+        <v>397.7326</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>-0.2961</v>
+        <v>-1.5913</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>-0.00376</v>
+        <v>-0.02039</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>1.2696</v>
+        <v>1.2816</v>
       </c>
     </row>
     <row r="39">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>INE119A01028</t>
+          <t>INE949H01023</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Limited</t>
+          <t>Man Infraconstruction Limited</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2433,34 +2433,34 @@
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>7209851</v>
+        <v>37148453</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>534.2</v>
+        <v>104.38</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>385.1502</v>
+        <v>387.7556</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>534.2</v>
+        <v>104.38</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>385.1502</v>
+        <v>387.7556</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>536.8</v>
+        <v>104.69</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>387.0248</v>
+        <v>388.9072</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>-0.4844</v>
+        <v>-0.2961</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>-0.00611</v>
+        <v>-0.00376</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>1.2611</v>
+        <v>1.2696</v>
       </c>
     </row>
     <row r="40">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>INE814H01029</t>
+          <t>INE002A01018</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Adani Power Limited</t>
+          <t>Reliance Industries Limited</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2484,38 +2484,38 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>14750325</v>
+        <v>2864589</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>229.27</v>
+        <v>1318.1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>338.1807</v>
+        <v>377.5815</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>229.27</v>
+        <v>1318.1</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>338.1807</v>
+        <v>377.5815</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>229.76</v>
+        <v>1313.6</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>338.9035</v>
+        <v>376.2924</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>-0.2133</v>
+        <v>0.3426</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>-0.00236</v>
+        <v>0.00424</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>1.1073</v>
+        <v>1.2363</v>
       </c>
     </row>
     <row r="41">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>INE807F01027</t>
+          <t>INE647O01011</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Viyash Scientific Limited</t>
+          <t>Aditya Birla Fashion And Retail Ltd</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2539,38 +2539,38 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>12557769</v>
+        <v>62138056</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>269.3</v>
+        <v>60.12</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>338.1807</v>
+        <v>373.574</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>269.3</v>
+        <v>60.12</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>338.1807</v>
+        <v>373.574</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>271.25</v>
+        <v>61.6</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>340.6295</v>
+        <v>382.7704</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>-0.7189</v>
+        <v>-2.4026</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>-0.00796</v>
+        <v>-0.02939</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>1.1073</v>
+        <v>1.2232</v>
       </c>
     </row>
     <row r="42">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>INE069I01010</t>
+          <t>INE074A01025</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Embassy Developments Limited</t>
+          <t>Praj Industries Limited</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2594,38 +2594,38 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>50672591</v>
+        <v>10680658</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>63.71</v>
+        <v>348.65</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>322.8351</v>
+        <v>372.3811</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>63.71</v>
+        <v>348.65</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>322.8351</v>
+        <v>372.3811</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>61.71</v>
+        <v>348.05</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>312.7006</v>
+        <v>371.7403</v>
       </c>
       <c r="M42" s="9" t="n">
-        <v>3.241</v>
+        <v>0.1724</v>
       </c>
       <c r="N42" s="10" t="n">
-        <v>0.03426</v>
+        <v>0.0021</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>1.0571</v>
+        <v>1.2193</v>
       </c>
     </row>
     <row r="43">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>INE322A01010</t>
+          <t>INE930H01031</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Gillette India Ltd</t>
+          <t>K.P.R. Mill Limited</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2653,34 +2653,34 @@
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>413737</v>
+        <v>3097567</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>7719</v>
+        <v>1191.3</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>319.3636</v>
+        <v>369.0132</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>7719</v>
+        <v>1191.3</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>319.3636</v>
+        <v>369.0132</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>7793</v>
+        <v>1218.45</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>322.4252</v>
+        <v>377.4231</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>-0.9496</v>
+        <v>-2.2282</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>-0.00993</v>
+        <v>-0.02692</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>1.0457</v>
+        <v>1.2083</v>
       </c>
     </row>
     <row r="44">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>INE0UIZ01018</t>
+          <t>INE821I01022</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>BLACKBUCK LIMITED</t>
+          <t>IRB Infrastructure Developers Limited</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2708,34 +2708,34 @@
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>5341242</v>
+        <v>171282204</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>562.8</v>
+        <v>21.19</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>300.6051</v>
+        <v>362.947</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>562.8</v>
+        <v>21.19</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>300.6051</v>
+        <v>362.947</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>561.5</v>
+        <v>21.32</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>299.9107</v>
+        <v>365.1737</v>
       </c>
       <c r="M44" s="9" t="n">
-        <v>0.2315</v>
+        <v>-0.6098</v>
       </c>
       <c r="N44" s="10" t="n">
-        <v>0.00228</v>
+        <v>-0.00725</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>0.9843</v>
+        <v>1.1884</v>
       </c>
     </row>
     <row r="45">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>INE073K01018</t>
+          <t>INE172A01027</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Sona BLW Precision Forgings Limited</t>
+          <t>Castrol India Limited</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2763,34 +2763,34 @@
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>4550945</v>
+        <v>19579007</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>619.25</v>
+        <v>185.37</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>281.8173</v>
+        <v>362.9361</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>619.25</v>
+        <v>185.37</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>281.8173</v>
+        <v>362.9361</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>619.2999</v>
+        <v>187.68</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>281.84</v>
+        <v>367.4588</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>-0.0081</v>
+        <v>-1.2308</v>
       </c>
       <c r="N45" s="10" t="n">
-        <v>-6.999999999999999e-05</v>
+        <v>-0.01463</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>0.9228</v>
+        <v>1.1884</v>
       </c>
     </row>
     <row r="46">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>INE172A01027</t>
+          <t>INE877F01012</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Castrol India Limited</t>
+          <t>PTC India Limited</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2818,34 +2818,34 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>15202959</v>
+        <v>19950003</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>185.37</v>
+        <v>181.8</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>281.8173</v>
+        <v>362.6911</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>185.37</v>
+        <v>181.8</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>281.8173</v>
+        <v>362.6911</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>187.68</v>
+        <v>184.76</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>285.3291</v>
+        <v>368.5963</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>-1.2308</v>
+        <v>-1.6021</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>-0.01136</v>
+        <v>-0.01903</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>0.9228</v>
+        <v>1.1876</v>
       </c>
     </row>
     <row r="47">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>INE0H9F01037</t>
+          <t>INE205C01021</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Sai Parenterals Limited</t>
+          <t>Poly Medicure Limited</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2873,34 +2873,34 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>4747738</v>
+        <v>2173543</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>585.3</v>
+        <v>1650.2</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>277.8851</v>
+        <v>358.6781</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>585.3</v>
+        <v>1650.2</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>277.8851</v>
+        <v>358.6781</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>589.75</v>
+        <v>1650.9</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>279.9978</v>
+        <v>358.8302</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>-0.7546</v>
+        <v>-0.0424</v>
       </c>
       <c r="N47" s="10" t="n">
-        <v>-0.00687</v>
+        <v>-0.0005</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>0.9099</v>
+        <v>1.1744</v>
       </c>
     </row>
     <row r="48">
@@ -2909,12 +2909,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>INE877F01012</t>
+          <t>INE795G01014</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>PTC India Limited</t>
+          <t>HDFC Life Insurance Co Ltd</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2924,38 +2924,38 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>14468066</v>
+        <v>5549244</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>181.8</v>
+        <v>585.45</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>263.0294</v>
+        <v>324.8805</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>181.8</v>
+        <v>585.45</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>263.0294</v>
+        <v>324.8805</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>184.76</v>
+        <v>591.75</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>267.312</v>
+        <v>328.3765</v>
       </c>
       <c r="M48" s="9" t="n">
-        <v>-1.6021</v>
+        <v>-1.0646</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>-0.0138</v>
+        <v>-0.01133</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>0.8613</v>
+        <v>1.0638</v>
       </c>
     </row>
     <row r="49">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>INE255A01020</t>
+          <t>INE306R01017</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>EPL Limited</t>
+          <t>Intellect Design Arena Limited</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2983,34 +2983,34 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>10748340</v>
+        <v>4331372</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>229.22</v>
+        <v>747.05</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>246.3734</v>
+        <v>323.5751</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>229.22</v>
+        <v>747.05</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>246.3734</v>
+        <v>323.5751</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>230.75</v>
+        <v>755.35</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>248.0179</v>
+        <v>327.1702</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>-0.6631</v>
+        <v>-1.0988</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>-0.00535</v>
+        <v>-0.01164</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>0.8067</v>
+        <v>1.0595</v>
       </c>
     </row>
     <row r="50">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>INE768C01028</t>
+          <t>INE868B01028</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Zydus Wellness Ltd</t>
+          <t>NCC Ltd</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3034,38 +3034,38 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>4744096</v>
+        <v>21043899</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>518.1</v>
+        <v>153.59</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>245.7916</v>
+        <v>323.2132</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>518.1</v>
+        <v>153.59</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>245.7916</v>
+        <v>323.2132</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>525.55</v>
+        <v>157.57</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>249.326</v>
+        <v>331.5887</v>
       </c>
       <c r="M50" s="9" t="n">
-        <v>-1.4176</v>
+        <v>-2.5259</v>
       </c>
       <c r="N50" s="10" t="n">
-        <v>-0.01141</v>
+        <v>-0.02673</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>0.8048</v>
+        <v>1.0583</v>
       </c>
     </row>
     <row r="51">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>INE821I01022</t>
+          <t>INE069I01010</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>IRB Infrastructure Developers Limited</t>
+          <t>Embassy Developments Limited</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3089,38 +3089,38 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>115262682</v>
+        <v>50672591</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>21.19</v>
+        <v>63.71</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>244.2416</v>
+        <v>322.8351</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>21.19</v>
+        <v>63.71</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>244.2416</v>
+        <v>322.8351</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>21.32</v>
+        <v>61.71</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>245.74</v>
+        <v>312.7006</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>-0.6098</v>
+        <v>3.241</v>
       </c>
       <c r="N51" s="10" t="n">
-        <v>-0.00488</v>
+        <v>0.03426</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>0.7997</v>
+        <v>1.0571</v>
       </c>
     </row>
     <row r="52">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>INE176A01028</t>
+          <t>INE322A01010</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Bata India Ltd</t>
+          <t>Gillette India Ltd</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3148,34 +3148,34 @@
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>3300826</v>
+        <v>413737</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>715.1</v>
+        <v>7719</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>236.0421</v>
+        <v>319.3636</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>715.1</v>
+        <v>7719</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>236.0421</v>
+        <v>319.3636</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>715</v>
+        <v>7793</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>236.0091</v>
+        <v>322.4252</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>0.014</v>
+        <v>-0.9496</v>
       </c>
       <c r="N52" s="10" t="n">
-        <v>0.00011</v>
+        <v>-0.00993</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>0.7729</v>
+        <v>1.0457</v>
       </c>
     </row>
     <row r="53">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>INE625G01013</t>
+          <t>INE302A01020</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Welspun Enterprises Limited</t>
+          <t>Exide Industries Limited</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3199,38 +3199,38 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3991315</v>
+        <v>8052582</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>572.45</v>
+        <v>389.8</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>228.4828</v>
+        <v>313.8896</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>572.45</v>
+        <v>389.8</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>228.4828</v>
+        <v>313.8896</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>569.05</v>
+        <v>399.5</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>227.1258</v>
+        <v>321.7007</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.5975</v>
+        <v>-2.428</v>
       </c>
       <c r="N53" s="10" t="n">
-        <v>0.00447</v>
+        <v>-0.02495</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>0.7481</v>
+        <v>1.0278</v>
       </c>
     </row>
     <row r="54">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>INE206N01018</t>
+          <t>INE0QPI01025</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Ravindra Energy Limited</t>
+          <t>Sudeep Pharma Limited</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3254,38 +3254,38 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>13937994</v>
+        <v>3777409</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>161.5</v>
+        <v>809.2</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>225.0986</v>
+        <v>305.6679</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>161.5</v>
+        <v>809.2</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>225.0986</v>
+        <v>305.6679</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>159.43</v>
+        <v>850.95</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>222.2134</v>
+        <v>321.4386</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>1.2984</v>
+        <v>-4.9063</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0.00957</v>
+        <v>-0.04911</v>
       </c>
       <c r="O54" s="9" t="n">
-        <v>0.7371</v>
+        <v>1.0009</v>
       </c>
     </row>
     <row r="55">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>INE429E01023</t>
+          <t>INE0H9F01037</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Safari Industries (India) Limited</t>
+          <t>Sai Parenterals Limited</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3309,38 +3309,38 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>1367670</v>
+        <v>4747738</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>1590.6</v>
+        <v>585.3</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>217.5416</v>
+        <v>277.8851</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>1590.6</v>
+        <v>585.3</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>217.5416</v>
+        <v>277.8851</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>1598.7</v>
+        <v>589.75</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>218.6494</v>
+        <v>279.9978</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>-0.5067</v>
+        <v>-0.7546</v>
       </c>
       <c r="N55" s="10" t="n">
-        <v>-0.00361</v>
+        <v>-0.00687</v>
       </c>
       <c r="O55" s="9" t="n">
-        <v>0.7123</v>
+        <v>0.9099</v>
       </c>
     </row>
     <row r="56">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>INE462A01022</t>
+          <t>INE0UIZ01018</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Bayer Cropscience Ltd</t>
+          <t>BLACKBUCK LIMITED</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3368,34 +3368,34 @@
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>501929</v>
+        <v>4845320</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>4186.3</v>
+        <v>562.8</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>210.1225</v>
+        <v>272.6946</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>4186.3</v>
+        <v>562.8</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>210.1225</v>
+        <v>272.6946</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>4199.3</v>
+        <v>561.5</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>210.775</v>
+        <v>272.0647</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>-0.3096</v>
+        <v>0.2315</v>
       </c>
       <c r="N56" s="10" t="n">
-        <v>-0.00213</v>
+        <v>0.00207</v>
       </c>
       <c r="O56" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="57">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>INE371A01025</t>
+          <t>INE438A01022</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Graphite India Limited</t>
+          <t>Apollo Tyres Ltd</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3423,34 +3423,34 @@
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>3256390</v>
+        <v>6253909</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>605.8</v>
+        <v>430.65</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>197.2721</v>
+        <v>269.3246</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>605.8</v>
+        <v>430.65</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>197.2721</v>
+        <v>269.3246</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>622.85</v>
+        <v>421.8</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>202.8243</v>
+        <v>263.7899</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>-2.7374</v>
+        <v>2.0982</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>-0.01768</v>
+        <v>0.0185</v>
       </c>
       <c r="O57" s="9" t="n">
-        <v>0.6459</v>
+        <v>0.8819</v>
       </c>
     </row>
     <row r="58">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>INE619B01017</t>
+          <t>INE126A01031</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Newgen Software Technologies Limited</t>
+          <t>EID Parry (India) Ltd</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>4169776</v>
+        <v>3767733</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>473.1</v>
+        <v>709.75</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>197.2721</v>
+        <v>267.4148</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>473.1</v>
+        <v>709.75</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>197.2721</v>
+        <v>267.4148</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>472.6</v>
+        <v>710.4</v>
       </c>
       <c r="L58" s="8" t="n">
-        <v>197.0636</v>
+        <v>267.6598</v>
       </c>
       <c r="M58" s="9" t="n">
-        <v>0.1058</v>
+        <v>-0.0915</v>
       </c>
       <c r="N58" s="10" t="n">
-        <v>0.00068</v>
+        <v>-0.0008</v>
       </c>
       <c r="O58" s="9" t="n">
-        <v>0.6459</v>
+        <v>0.8756</v>
       </c>
     </row>
     <row r="59">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>INE424H01027</t>
+          <t>INE095N01031</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>SUN TV Network Limited</t>
+          <t>National Building Construction Corp</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3529,38 +3529,38 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>3779214</v>
+        <v>24265988</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>513.5</v>
+        <v>107.17</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>194.0626</v>
+        <v>260.0586</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>513.5</v>
+        <v>107.17</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>194.0626</v>
+        <v>260.0586</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>516.85</v>
+        <v>108.88</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>195.3287</v>
+        <v>264.2081</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>-0.6482</v>
+        <v>-1.5705</v>
       </c>
       <c r="N59" s="10" t="n">
-        <v>-0.00412</v>
+        <v>-0.01337</v>
       </c>
       <c r="O59" s="9" t="n">
-        <v>0.6354</v>
+        <v>0.8515</v>
       </c>
     </row>
     <row r="60">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>INE026A01025</t>
+          <t>INE255A01020</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Gujarat State Fert &amp; Chemicals Ltd</t>
+          <t>EPL Limited</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3588,34 +3588,34 @@
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>11005162</v>
+        <v>10748340</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>163.13</v>
+        <v>229.22</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>179.5272</v>
+        <v>246.3734</v>
       </c>
       <c r="I60" s="7" t="n">
-        <v>163.13</v>
+        <v>229.22</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>179.5272</v>
+        <v>246.3734</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>163.9</v>
+        <v>230.75</v>
       </c>
       <c r="L60" s="8" t="n">
-        <v>180.3746</v>
+        <v>248.0179</v>
       </c>
       <c r="M60" s="9" t="n">
-        <v>-0.4698</v>
+        <v>-0.6631</v>
       </c>
       <c r="N60" s="10" t="n">
-        <v>-0.00276</v>
+        <v>-0.00535</v>
       </c>
       <c r="O60" s="9" t="n">
-        <v>0.5878</v>
+        <v>0.8067</v>
       </c>
     </row>
     <row r="61">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>INE463V01026</t>
+          <t>INE768C01028</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Anand Rathi Wealth Limited</t>
+          <t>Zydus Wellness Ltd</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3639,38 +3639,38 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>923593</v>
+        <v>4744096</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>1932.5</v>
+        <v>518.1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>178.4843</v>
+        <v>245.7916</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>1932.5</v>
+        <v>518.1</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>178.4843</v>
+        <v>245.7916</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>1903.9</v>
+        <v>525.55</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>175.8429</v>
+        <v>249.326</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>1.5022</v>
+        <v>-1.4176</v>
       </c>
       <c r="N61" s="10" t="n">
-        <v>0.00878</v>
+        <v>-0.01141</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>0.5844</v>
+        <v>0.8048</v>
       </c>
     </row>
     <row r="62">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>INE00E101023</t>
+          <t>INE176A01028</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Bikaji Foods International Limited</t>
+          <t>Bata India Ltd</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3694,38 +3694,38 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>2643302</v>
+        <v>3300826</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>640.6</v>
+        <v>715.1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>169.3299</v>
+        <v>236.0421</v>
       </c>
       <c r="I62" s="7" t="n">
-        <v>640.6</v>
+        <v>715.1</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>169.3299</v>
+        <v>236.0421</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>650.95</v>
+        <v>715</v>
       </c>
       <c r="L62" s="8" t="n">
-        <v>172.0657</v>
+        <v>236.0091</v>
       </c>
       <c r="M62" s="9" t="n">
-        <v>-1.59</v>
+        <v>0.014</v>
       </c>
       <c r="N62" s="10" t="n">
-        <v>-0.00881</v>
+        <v>0.00011</v>
       </c>
       <c r="O62" s="9" t="n">
-        <v>0.5544</v>
+        <v>0.7729</v>
       </c>
     </row>
     <row r="63">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>INE438A01022</t>
+          <t>INE625G01013</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Apollo Tyres Ltd</t>
+          <t>Welspun Enterprises Limited</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3749,38 +3749,38 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>3926399</v>
+        <v>3991315</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>430.65</v>
+        <v>572.45</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>169.0904</v>
+        <v>228.4828</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>430.65</v>
+        <v>572.45</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>169.0904</v>
+        <v>228.4828</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>421.8</v>
+        <v>569.05</v>
       </c>
       <c r="L63" s="8" t="n">
-        <v>165.6155</v>
+        <v>227.1258</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>2.0982</v>
+        <v>0.5975</v>
       </c>
       <c r="N63" s="10" t="n">
-        <v>0.01162</v>
+        <v>0.00447</v>
       </c>
       <c r="O63" s="9" t="n">
-        <v>0.5537</v>
+        <v>0.7481</v>
       </c>
     </row>
     <row r="64">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>INE182A01018</t>
+          <t>INE206N01018</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Pfizer Ltd</t>
+          <t>Ravindra Energy Limited</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3808,34 +3808,34 @@
         </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>365323</v>
+        <v>13937994</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>4460.7</v>
+        <v>161.5</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>162.9596</v>
+        <v>225.0986</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>4460.7</v>
+        <v>161.5</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>162.9596</v>
+        <v>225.0986</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>4507.2</v>
+        <v>159.43</v>
       </c>
       <c r="L64" s="8" t="n">
-        <v>164.6584</v>
+        <v>222.2134</v>
       </c>
       <c r="M64" s="9" t="n">
-        <v>-1.0317</v>
+        <v>1.2984</v>
       </c>
       <c r="N64" s="10" t="n">
-        <v>-0.00551</v>
+        <v>0.00957</v>
       </c>
       <c r="O64" s="9" t="n">
-        <v>0.5336</v>
+        <v>0.7371</v>
       </c>
     </row>
     <row r="65">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>INE14LE01019</t>
+          <t>INE462A01022</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Aditya Birla Lifestyle Brands Limited</t>
+          <t>Bayer Cropscience Ltd</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3859,38 +3859,38 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>16455992</v>
+        <v>501929</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>97.56999999999999</v>
+        <v>4186.3</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>160.5611</v>
+        <v>210.1225</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>97.56999999999999</v>
+        <v>4186.3</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>160.5611</v>
+        <v>210.1225</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>100.48</v>
+        <v>4199.3</v>
       </c>
       <c r="L65" s="8" t="n">
-        <v>165.3498</v>
+        <v>210.775</v>
       </c>
       <c r="M65" s="9" t="n">
-        <v>-2.8961</v>
+        <v>-0.3096</v>
       </c>
       <c r="N65" s="10" t="n">
-        <v>-0.01522</v>
+        <v>-0.00213</v>
       </c>
       <c r="O65" s="9" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>INE095N01031</t>
+          <t>INE424H01027</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>National Building Construction Corp</t>
+          <t>SUN TV Network Limited</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3914,38 +3914,38 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>14901227</v>
+        <v>3779214</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>107.17</v>
+        <v>513.5</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>159.6964</v>
+        <v>194.0626</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>107.17</v>
+        <v>513.5</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>159.6964</v>
+        <v>194.0626</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>108.88</v>
+        <v>516.85</v>
       </c>
       <c r="L66" s="8" t="n">
-        <v>162.2446</v>
+        <v>195.3287</v>
       </c>
       <c r="M66" s="9" t="n">
-        <v>-1.5705</v>
+        <v>-0.6482</v>
       </c>
       <c r="N66" s="10" t="n">
-        <v>-0.00821</v>
+        <v>-0.00412</v>
       </c>
       <c r="O66" s="9" t="n">
-        <v>0.5229</v>
+        <v>0.6354</v>
       </c>
     </row>
     <row r="67">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>INE126A01031</t>
+          <t>INE026A01025</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>EID Parry (India) Ltd</t>
+          <t>Gujarat State Fert &amp; Chemicals Ltd</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3969,38 +3969,38 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>2250038</v>
+        <v>11005162</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>709.75</v>
+        <v>163.13</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>159.6964</v>
+        <v>179.5272</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>709.75</v>
+        <v>163.13</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>159.6964</v>
+        <v>179.5272</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>710.4</v>
+        <v>163.9</v>
       </c>
       <c r="L67" s="8" t="n">
-        <v>159.8427</v>
+        <v>180.3746</v>
       </c>
       <c r="M67" s="9" t="n">
-        <v>-0.0915</v>
+        <v>-0.4698</v>
       </c>
       <c r="N67" s="10" t="n">
-        <v>-0.00048</v>
+        <v>-0.00276</v>
       </c>
       <c r="O67" s="9" t="n">
-        <v>0.5229</v>
+        <v>0.5878</v>
       </c>
     </row>
     <row r="68">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>INE700A01033</t>
+          <t>INE00E101023</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Jubilant Pharmova Limited</t>
+          <t>Bikaji Foods International Limited</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -4028,34 +4028,34 @@
         </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1639624</v>
+        <v>2643302</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>964.4</v>
+        <v>640.6</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>158.1253</v>
+        <v>169.3299</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>964.4</v>
+        <v>640.6</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>158.1253</v>
+        <v>169.3299</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>972.8</v>
+        <v>650.95</v>
       </c>
       <c r="L68" s="8" t="n">
-        <v>159.5026</v>
+        <v>172.0657</v>
       </c>
       <c r="M68" s="9" t="n">
-        <v>-0.8635</v>
+        <v>-1.59</v>
       </c>
       <c r="N68" s="10" t="n">
-        <v>-0.00447</v>
+        <v>-0.00881</v>
       </c>
       <c r="O68" s="9" t="n">
-        <v>0.5178</v>
+        <v>0.5544</v>
       </c>
     </row>
     <row r="69">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>INE03Q201024</t>
+          <t>INE182A01018</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Alivus Life Sciences</t>
+          <t>Pfizer Ltd</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -4079,38 +4079,38 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1396340</v>
+        <v>365323</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>1108.3</v>
+        <v>4460.7</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>154.7564</v>
+        <v>162.9596</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>1108.3</v>
+        <v>4460.7</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>154.7564</v>
+        <v>162.9596</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>1116.1</v>
+        <v>4507.2</v>
       </c>
       <c r="L69" s="8" t="n">
-        <v>155.8455</v>
+        <v>164.6584</v>
       </c>
       <c r="M69" s="9" t="n">
-        <v>-0.6989</v>
+        <v>-1.0317</v>
       </c>
       <c r="N69" s="10" t="n">
-        <v>-0.00354</v>
+        <v>-0.00551</v>
       </c>
       <c r="O69" s="9" t="n">
-        <v>0.5067</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="70">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>INE438K01021</t>
+          <t>INE14LE01019</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Sai Silks (Kalamandir) Limited</t>
+          <t>Aditya Birla Lifestyle Brands Limited</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -4138,34 +4138,34 @@
         </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>13788126</v>
+        <v>16455992</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>109.98</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>151.6418</v>
+        <v>160.5611</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>109.98</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="J70" s="8" t="n">
-        <v>151.6418</v>
+        <v>160.5611</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>109.55</v>
+        <v>100.48</v>
       </c>
       <c r="L70" s="8" t="n">
-        <v>151.0489</v>
+        <v>165.3498</v>
       </c>
       <c r="M70" s="9" t="n">
-        <v>0.3925</v>
+        <v>-2.8961</v>
       </c>
       <c r="N70" s="10" t="n">
-        <v>0.00195</v>
+        <v>-0.01522</v>
       </c>
       <c r="O70" s="9" t="n">
-        <v>0.4965</v>
+        <v>0.5256999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>INE0N2P01017</t>
+          <t>INE700A01033</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>RISHABH INSTRUMENTS LIMITED</t>
+          <t>Jubilant Pharmova Limited</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -4189,38 +4189,38 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F71" s="6" t="n">
-        <v>2659083</v>
+        <v>1639624</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>567.4</v>
+        <v>964.4</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>150.8764</v>
+        <v>158.1253</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>567.4</v>
+        <v>964.4</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>150.8764</v>
+        <v>158.1253</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>585.05</v>
+        <v>972.8</v>
       </c>
       <c r="L71" s="8" t="n">
-        <v>155.5697</v>
+        <v>159.5026</v>
       </c>
       <c r="M71" s="9" t="n">
-        <v>-3.0168</v>
+        <v>-0.8635</v>
       </c>
       <c r="N71" s="10" t="n">
-        <v>-0.0149</v>
+        <v>-0.00447</v>
       </c>
       <c r="O71" s="9" t="n">
-        <v>0.494</v>
+        <v>0.5178</v>
       </c>
     </row>
     <row r="72">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>INE058A01010</t>
+          <t>INE03Q201024</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>SANOFI INDIA LIMITED</t>
+          <t>Alivus Life Sciences</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -4244,38 +4244,38 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>441919</v>
+        <v>1396340</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>3355.6</v>
+        <v>1108.3</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>148.2903</v>
+        <v>154.7564</v>
       </c>
       <c r="I72" s="7" t="n">
-        <v>3355.6</v>
+        <v>1108.3</v>
       </c>
       <c r="J72" s="8" t="n">
-        <v>148.2903</v>
+        <v>154.7564</v>
       </c>
       <c r="K72" s="7" t="n">
-        <v>3399.2</v>
+        <v>1116.1</v>
       </c>
       <c r="L72" s="8" t="n">
-        <v>150.2171</v>
+        <v>155.8455</v>
       </c>
       <c r="M72" s="9" t="n">
-        <v>-1.2827</v>
+        <v>-0.6989</v>
       </c>
       <c r="N72" s="10" t="n">
-        <v>-0.00623</v>
+        <v>-0.00354</v>
       </c>
       <c r="O72" s="9" t="n">
-        <v>0.4856</v>
+        <v>0.5067</v>
       </c>
     </row>
     <row r="73">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>INE978A01027</t>
+          <t>INE438K01021</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Heritage Foods Limited</t>
+          <t>Sai Silks (Kalamandir) Limited</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -4299,38 +4299,38 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>3980866</v>
+        <v>13788126</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>336.8</v>
+        <v>109.98</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>134.0756</v>
+        <v>151.6418</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>336.8</v>
+        <v>109.98</v>
       </c>
       <c r="J73" s="8" t="n">
-        <v>134.0756</v>
+        <v>151.6418</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>320.8</v>
+        <v>109.55</v>
       </c>
       <c r="L73" s="8" t="n">
-        <v>127.7062</v>
+        <v>151.0489</v>
       </c>
       <c r="M73" s="9" t="n">
-        <v>4.9875</v>
+        <v>0.3925</v>
       </c>
       <c r="N73" s="10" t="n">
-        <v>0.0219</v>
+        <v>0.00195</v>
       </c>
       <c r="O73" s="9" t="n">
-        <v>0.439</v>
+        <v>0.4965</v>
       </c>
     </row>
     <row r="74">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>INE229H01012</t>
+          <t>INE0N2P01017</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Nitin Spinners Limited</t>
+          <t>RISHABH INSTRUMENTS LIMITED</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -4358,34 +4358,34 @@
         </is>
       </c>
       <c r="F74" s="6" t="n">
-        <v>2346803</v>
+        <v>2659083</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>550.4</v>
+        <v>567.4</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>129.168</v>
+        <v>150.8764</v>
       </c>
       <c r="I74" s="7" t="n">
-        <v>550.4</v>
+        <v>567.4</v>
       </c>
       <c r="J74" s="8" t="n">
-        <v>129.168</v>
+        <v>150.8764</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>567.3</v>
+        <v>585.05</v>
       </c>
       <c r="L74" s="8" t="n">
-        <v>133.1341</v>
+        <v>155.5697</v>
       </c>
       <c r="M74" s="9" t="n">
-        <v>-2.979</v>
+        <v>-3.0168</v>
       </c>
       <c r="N74" s="10" t="n">
-        <v>-0.0126</v>
+        <v>-0.0149</v>
       </c>
       <c r="O74" s="9" t="n">
-        <v>0.4229</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="75">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>INE271B01025</t>
+          <t>INE058A01010</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Maharashtra Seamless Ltd</t>
+          <t>SANOFI INDIA LIMITED</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -4413,34 +4413,34 @@
         </is>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1885445</v>
+        <v>441919</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>628.4</v>
+        <v>3355.6</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>118.4814</v>
+        <v>148.2903</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>628.4</v>
+        <v>3355.6</v>
       </c>
       <c r="J75" s="8" t="n">
-        <v>118.4814</v>
+        <v>148.2903</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>648.8</v>
+        <v>3399.2</v>
       </c>
       <c r="L75" s="8" t="n">
-        <v>122.3277</v>
+        <v>150.2171</v>
       </c>
       <c r="M75" s="9" t="n">
-        <v>-3.1443</v>
+        <v>-1.2827</v>
       </c>
       <c r="N75" s="10" t="n">
-        <v>-0.0122</v>
+        <v>-0.00623</v>
       </c>
       <c r="O75" s="9" t="n">
-        <v>0.3879</v>
+        <v>0.4856</v>
       </c>
     </row>
     <row r="76">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>INE599M01018</t>
+          <t>INE229H01012</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Just Dial Limited</t>
+          <t>Nitin Spinners Limited</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4464,38 +4464,38 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>2164484</v>
+        <v>2346803</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>537.7</v>
+        <v>550.4</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>116.3843</v>
+        <v>129.168</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>537.7</v>
+        <v>550.4</v>
       </c>
       <c r="J76" s="8" t="n">
-        <v>116.3843</v>
+        <v>129.168</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>550.9</v>
+        <v>567.3</v>
       </c>
       <c r="L76" s="8" t="n">
-        <v>119.2414</v>
+        <v>133.1341</v>
       </c>
       <c r="M76" s="9" t="n">
-        <v>-2.3961</v>
+        <v>-2.979</v>
       </c>
       <c r="N76" s="10" t="n">
-        <v>-0.009129999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="O76" s="9" t="n">
-        <v>0.3811</v>
+        <v>0.4229</v>
       </c>
     </row>
     <row r="77">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>INE998I01010</t>
+          <t>INE271B01025</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Mahindra Holidays &amp; Resorts Ind Ltd</t>
+          <t>Maharashtra Seamless Ltd</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -4519,38 +4519,38 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F77" s="6" t="n">
-        <v>4618825</v>
+        <v>1885445</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>240.06</v>
+        <v>628.4</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>110.8795</v>
+        <v>118.4814</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>240.06</v>
+        <v>628.4</v>
       </c>
       <c r="J77" s="8" t="n">
-        <v>110.8795</v>
+        <v>118.4814</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>239.53</v>
+        <v>648.8</v>
       </c>
       <c r="L77" s="8" t="n">
-        <v>110.6347</v>
+        <v>122.3277</v>
       </c>
       <c r="M77" s="9" t="n">
-        <v>0.2213</v>
+        <v>-3.1443</v>
       </c>
       <c r="N77" s="10" t="n">
-        <v>0.0008</v>
+        <v>-0.0122</v>
       </c>
       <c r="O77" s="9" t="n">
-        <v>0.3631</v>
+        <v>0.3879</v>
       </c>
     </row>
     <row r="78">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>INE812G01025</t>
+          <t>INE599M01018</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>SMS Pharmaceuticals Limited</t>
+          <t>Just Dial Limited</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -4578,34 +4578,34 @@
         </is>
       </c>
       <c r="F78" s="6" t="n">
-        <v>2593308</v>
+        <v>2164484</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>376.55</v>
+        <v>537.7</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>97.651</v>
+        <v>116.3843</v>
       </c>
       <c r="I78" s="7" t="n">
-        <v>376.55</v>
+        <v>537.7</v>
       </c>
       <c r="J78" s="8" t="n">
-        <v>97.651</v>
+        <v>116.3843</v>
       </c>
       <c r="K78" s="7" t="n">
-        <v>378.5</v>
+        <v>550.9</v>
       </c>
       <c r="L78" s="8" t="n">
-        <v>98.1567</v>
+        <v>119.2414</v>
       </c>
       <c r="M78" s="9" t="n">
-        <v>-0.5152</v>
+        <v>-2.3961</v>
       </c>
       <c r="N78" s="10" t="n">
-        <v>-0.00165</v>
+        <v>-0.009129999999999999</v>
       </c>
       <c r="O78" s="9" t="n">
-        <v>0.3197</v>
+        <v>0.3811</v>
       </c>
     </row>
     <row r="79">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>INE750A01020</t>
+          <t>INE264T01014</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Oriental Hotels Limited</t>
+          <t>Capacite Infraprojects Limited</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -4629,38 +4629,38 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5260733</v>
+        <v>4273382</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>139.32</v>
+        <v>263.91</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>73.2925</v>
+        <v>112.7788</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>139.32</v>
+        <v>263.91</v>
       </c>
       <c r="J79" s="8" t="n">
-        <v>73.2925</v>
+        <v>112.7788</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>139.17</v>
+        <v>262.35</v>
       </c>
       <c r="L79" s="8" t="n">
-        <v>73.2136</v>
+        <v>112.1122</v>
       </c>
       <c r="M79" s="9" t="n">
-        <v>0.1078</v>
+        <v>0.5946</v>
       </c>
       <c r="N79" s="10" t="n">
-        <v>0.00026</v>
+        <v>0.0022</v>
       </c>
       <c r="O79" s="9" t="n">
-        <v>0.24</v>
+        <v>0.3693</v>
       </c>
     </row>
     <row r="80">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>INE212I01016</t>
+          <t>INE812G01025</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>S. P. Apparels Limited</t>
+          <t>SMS Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -4688,34 +4688,34 @@
         </is>
       </c>
       <c r="F80" s="6" t="n">
-        <v>586161</v>
+        <v>2593308</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>1099.95</v>
+        <v>376.55</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>64.4748</v>
+        <v>97.651</v>
       </c>
       <c r="I80" s="7" t="n">
-        <v>1099.95</v>
+        <v>376.55</v>
       </c>
       <c r="J80" s="8" t="n">
-        <v>64.4748</v>
+        <v>97.651</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>1109.1</v>
+        <v>378.5</v>
       </c>
       <c r="L80" s="8" t="n">
-        <v>65.0111</v>
+        <v>98.1567</v>
       </c>
       <c r="M80" s="9" t="n">
-        <v>-0.825</v>
+        <v>-0.5152</v>
       </c>
       <c r="N80" s="10" t="n">
-        <v>-0.00174</v>
+        <v>-0.00165</v>
       </c>
       <c r="O80" s="9" t="n">
-        <v>0.2111</v>
+        <v>0.3197</v>
       </c>
     </row>
     <row r="81">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>INE873D01024</t>
+          <t>INE750A01020</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>INDOCO REMEDIES LIMITED</t>
+          <t>Oriental Hotels Limited</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -4739,38 +4739,38 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F81" s="6" t="n">
-        <v>2623571</v>
+        <v>5260733</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>231.6</v>
+        <v>139.32</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>60.7619</v>
+        <v>73.2925</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>231.6</v>
+        <v>139.32</v>
       </c>
       <c r="J81" s="8" t="n">
-        <v>60.7619</v>
+        <v>73.2925</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>237.2</v>
+        <v>139.17</v>
       </c>
       <c r="L81" s="8" t="n">
-        <v>62.2311</v>
+        <v>73.2136</v>
       </c>
       <c r="M81" s="9" t="n">
-        <v>-2.3609</v>
+        <v>0.1078</v>
       </c>
       <c r="N81" s="10" t="n">
-        <v>-0.0047</v>
+        <v>0.00026</v>
       </c>
       <c r="O81" s="9" t="n">
-        <v>0.199</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="82">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>INE696F01016</t>
+          <t>INE212I01016</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Juniper Hotels Limited</t>
+          <t>S. P. Apparels Limited</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -4794,38 +4794,38 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F82" s="6" t="n">
-        <v>3080267</v>
+        <v>586161</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>196.7</v>
+        <v>1099.95</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>60.5889</v>
+        <v>64.4748</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>196.7</v>
+        <v>1099.95</v>
       </c>
       <c r="J82" s="8" t="n">
-        <v>60.5889</v>
+        <v>64.4748</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>199.34</v>
+        <v>1109.1</v>
       </c>
       <c r="L82" s="8" t="n">
-        <v>61.402</v>
+        <v>65.0111</v>
       </c>
       <c r="M82" s="9" t="n">
-        <v>-1.3244</v>
+        <v>-0.825</v>
       </c>
       <c r="N82" s="10" t="n">
-        <v>-0.00263</v>
+        <v>-0.00174</v>
       </c>
       <c r="O82" s="9" t="n">
-        <v>0.1984</v>
+        <v>0.2111</v>
       </c>
     </row>
     <row r="83">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>INE182D01020</t>
+          <t>INE696F01016</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Marathon Nextgen Realty Limited</t>
+          <t>Juniper Hotels Limited</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4849,38 +4849,38 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F83" s="6" t="n">
-        <v>1423790</v>
+        <v>3080267</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>405.1</v>
+        <v>196.7</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>57.6777</v>
+        <v>60.5889</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>405.1</v>
+        <v>196.7</v>
       </c>
       <c r="J83" s="8" t="n">
-        <v>57.6777</v>
+        <v>60.5889</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>406.75</v>
+        <v>199.34</v>
       </c>
       <c r="L83" s="8" t="n">
-        <v>57.9127</v>
+        <v>61.402</v>
       </c>
       <c r="M83" s="9" t="n">
-        <v>-0.4057</v>
+        <v>-1.3244</v>
       </c>
       <c r="N83" s="10" t="n">
-        <v>-0.00077</v>
+        <v>-0.00263</v>
       </c>
       <c r="O83" s="9" t="n">
-        <v>0.1889</v>
+        <v>0.1984</v>
       </c>
     </row>
     <row r="84">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>INE907A01026</t>
+          <t>INE182D01020</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Kalyani Steels Ltd</t>
+          <t>Marathon Nextgen Realty Limited</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4908,34 +4908,34 @@
         </is>
       </c>
       <c r="F84" s="6" t="n">
-        <v>650349</v>
+        <v>1423790</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>818.7</v>
+        <v>405.1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>53.2441</v>
+        <v>57.6777</v>
       </c>
       <c r="I84" s="7" t="n">
-        <v>818.7</v>
+        <v>405.1</v>
       </c>
       <c r="J84" s="8" t="n">
-        <v>53.2441</v>
+        <v>57.6777</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>826</v>
+        <v>406.75</v>
       </c>
       <c r="L84" s="8" t="n">
-        <v>53.7188</v>
+        <v>57.9127</v>
       </c>
       <c r="M84" s="9" t="n">
-        <v>-0.8838</v>
+        <v>-0.4057</v>
       </c>
       <c r="N84" s="10" t="n">
-        <v>-0.00154</v>
+        <v>-0.00077</v>
       </c>
       <c r="O84" s="9" t="n">
-        <v>0.1743</v>
+        <v>0.1889</v>
       </c>
     </row>
     <row r="85">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>INE04TZ01018</t>
+          <t>INE907A01026</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>ETHOS LIMITED</t>
+          <t>Kalyani Steels Ltd</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -4959,38 +4959,38 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>cyclical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F85" s="6" t="n">
-        <v>200023</v>
+        <v>650349</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>2436.9</v>
+        <v>818.7</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>48.7436</v>
+        <v>53.2441</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>2436.9</v>
+        <v>818.7</v>
       </c>
       <c r="J85" s="8" t="n">
-        <v>48.7436</v>
+        <v>53.2441</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>2416.9</v>
+        <v>826</v>
       </c>
       <c r="L85" s="8" t="n">
-        <v>48.3436</v>
+        <v>53.7188</v>
       </c>
       <c r="M85" s="9" t="n">
-        <v>0.8275</v>
+        <v>-0.8838</v>
       </c>
       <c r="N85" s="10" t="n">
-        <v>0.00132</v>
+        <v>-0.00154</v>
       </c>
       <c r="O85" s="9" t="n">
-        <v>0.1596</v>
+        <v>0.1743</v>
       </c>
     </row>
     <row r="86">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>INE725E01024</t>
+          <t>INE04TZ01018</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>The Orissa Minerals Development Co Ltd</t>
+          <t>ETHOS LIMITED</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -5014,38 +5014,38 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F86" s="6" t="n">
-        <v>120389</v>
+        <v>200023</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>3929.8</v>
+        <v>2436.9</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>47.3105</v>
+        <v>48.7436</v>
       </c>
       <c r="I86" s="7" t="n">
-        <v>3929.8</v>
+        <v>2436.9</v>
       </c>
       <c r="J86" s="8" t="n">
-        <v>47.3105</v>
+        <v>48.7436</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>3992.2</v>
+        <v>2416.9</v>
       </c>
       <c r="L86" s="8" t="n">
-        <v>48.0617</v>
+        <v>48.3436</v>
       </c>
       <c r="M86" s="9" t="n">
-        <v>-1.563</v>
+        <v>0.8275</v>
       </c>
       <c r="N86" s="10" t="n">
-        <v>-0.00242</v>
+        <v>0.00132</v>
       </c>
       <c r="O86" s="9" t="n">
-        <v>0.1549</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="87">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>INE0U4701011</t>
+          <t>INE725E01024</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Digitide Solutions Limited</t>
+          <t>The Orissa Minerals Development Co Ltd</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -5073,34 +5073,34 @@
         </is>
       </c>
       <c r="F87" s="6" t="n">
-        <v>4720102</v>
+        <v>120389</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>86.36</v>
+        <v>3929.8</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>40.7628</v>
+        <v>47.3105</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>86.36</v>
+        <v>3929.8</v>
       </c>
       <c r="J87" s="8" t="n">
-        <v>40.7628</v>
+        <v>47.3105</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>88.05</v>
+        <v>3992.2</v>
       </c>
       <c r="L87" s="8" t="n">
-        <v>41.5605</v>
+        <v>48.0617</v>
       </c>
       <c r="M87" s="9" t="n">
-        <v>-1.9194</v>
+        <v>-1.563</v>
       </c>
       <c r="N87" s="10" t="n">
-        <v>-0.00256</v>
+        <v>-0.00242</v>
       </c>
       <c r="O87" s="9" t="n">
-        <v>0.1335</v>
+        <v>0.1549</v>
       </c>
     </row>
     <row r="88">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>INE781S01027</t>
+          <t>INE988S01028</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Ventive Hospitality Limited</t>
+          <t>Apeejay Surrendra Park Hotels Limited</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -5179,38 +5179,38 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F89" s="6" t="n">
-        <v>509112</v>
+        <v>2985747</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>643.9</v>
+        <v>122.23</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>32.7817</v>
+        <v>36.4948</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>643.9</v>
+        <v>122.23</v>
       </c>
       <c r="J89" s="8" t="n">
-        <v>32.7817</v>
+        <v>36.4948</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>638.45</v>
+        <v>123.92</v>
       </c>
       <c r="L89" s="8" t="n">
-        <v>32.5043</v>
+        <v>36.9994</v>
       </c>
       <c r="M89" s="9" t="n">
-        <v>0.8536</v>
+        <v>-1.3638</v>
       </c>
       <c r="N89" s="10" t="n">
-        <v>0.00092</v>
+        <v>-0.00163</v>
       </c>
       <c r="O89" s="9" t="n">
-        <v>0.1073</v>
+        <v>0.1195</v>
       </c>
     </row>
     <row r="90">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>INE032B01021</t>
+          <t>INE781S01027</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Prime Securities Limited</t>
+          <t>Ventive Hospitality Limited</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -5238,34 +5238,34 @@
         </is>
       </c>
       <c r="F90" s="6" t="n">
-        <v>817007</v>
+        <v>509112</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>299.2</v>
+        <v>643.9</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>24.4448</v>
+        <v>32.7817</v>
       </c>
       <c r="I90" s="7" t="n">
-        <v>299.2</v>
+        <v>643.9</v>
       </c>
       <c r="J90" s="8" t="n">
-        <v>24.4448</v>
+        <v>32.7817</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>295</v>
+        <v>638.45</v>
       </c>
       <c r="L90" s="8" t="n">
-        <v>24.1017</v>
+        <v>32.5043</v>
       </c>
       <c r="M90" s="9" t="n">
-        <v>1.4237</v>
+        <v>0.8536</v>
       </c>
       <c r="N90" s="10" t="n">
-        <v>0.00114</v>
+        <v>0.00092</v>
       </c>
       <c r="O90" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="91">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>INE263M01029</t>
+          <t>INE032B01021</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>KEYSTONE REALTORS LIMITED</t>
+          <t>Prime Securities Limited</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -5293,34 +5293,34 @@
         </is>
       </c>
       <c r="F91" s="6" t="n">
-        <v>324020</v>
+        <v>817007</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>384.55</v>
+        <v>299.2</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>12.4602</v>
+        <v>24.4448</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>384.55</v>
+        <v>299.2</v>
       </c>
       <c r="J91" s="8" t="n">
-        <v>12.4602</v>
+        <v>24.4448</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>384.2</v>
+        <v>295</v>
       </c>
       <c r="L91" s="8" t="n">
-        <v>12.4488</v>
+        <v>24.1017</v>
       </c>
       <c r="M91" s="9" t="n">
-        <v>0.0911</v>
+        <v>1.4237</v>
       </c>
       <c r="N91" s="10" t="n">
-        <v>4e-05</v>
+        <v>0.00114</v>
       </c>
       <c r="O91" s="9" t="n">
-        <v>0.0408</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="92">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>INE0AE001013</t>
+          <t>INE263M01029</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Vishnu Prakash R Punglia Limited</t>
+          <t>KEYSTONE REALTORS LIMITED</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -5348,34 +5348,34 @@
         </is>
       </c>
       <c r="F92" s="6" t="n">
-        <v>4085609</v>
+        <v>324020</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>29.05</v>
+        <v>384.55</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>11.8687</v>
+        <v>12.4602</v>
       </c>
       <c r="I92" s="7" t="n">
-        <v>29.05</v>
+        <v>384.55</v>
       </c>
       <c r="J92" s="8" t="n">
-        <v>11.8687</v>
+        <v>12.4602</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>29.64</v>
+        <v>384.2</v>
       </c>
       <c r="L92" s="8" t="n">
-        <v>12.1097</v>
+        <v>12.4488</v>
       </c>
       <c r="M92" s="9" t="n">
-        <v>-1.9906</v>
+        <v>0.0911</v>
       </c>
       <c r="N92" s="10" t="n">
-        <v>-0.00077</v>
+        <v>4e-05</v>
       </c>
       <c r="O92" s="9" t="n">
-        <v>0.0389</v>
+        <v>0.0408</v>
       </c>
     </row>
     <row r="93">
@@ -5558,7 +5558,7 @@
       <c r="H96" s="11" t="n"/>
       <c r="I96" s="11" t="n"/>
       <c r="J96" s="13" t="n">
-        <v>29013.379</v>
+        <v>29013.38</v>
       </c>
       <c r="K96" s="11" t="n"/>
       <c r="L96" s="11" t="n"/>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="C102" s="15" t="n">
-        <v>0.1408</v>
+        <v>-0.0585</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
